--- a/docs/test-cases.xlsx
+++ b/docs/test-cases.xlsx
@@ -279,7 +279,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-05-02</t>
+    <t>2026-05-04</t>
   </si>
 </sst>
 </file>
